--- a/output/pdf_financials_xlsx/EXN.xlsx
+++ b/output/pdf_financials_xlsx/EXN.xlsx
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.737038</v>
+        <v>-0.737038</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-3.865</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.737038</v>
+        <v>-0.737038</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-3.865</v>
@@ -2001,16 +2001,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.935134</v>
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2.65011</v>
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2.499</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2.893</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -2058,16 +2058,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.60073</v>
+        <v>1.665596</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.70889</v>
+        <v>-5.359</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>13.745</v>
+        <v>11.246</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.399</v>
+        <v>0.506</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-3.618</v>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>16.2224623027185</v>
+        <v>10.38941694122755</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-9.218928668663217</v>
+        <v>-18.23781649877484</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>28.62945219745886</v>
+        <v>23.42428660695688</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>9.370606236043338</v>
+        <v>1.394976980122956</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-10.85443417736709</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>4.597390413718854</v>
+        <v>-4.597390413718854</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>-13.15341682548326</v>
@@ -6080,13 +6080,13 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>2.532</v>
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>2.499</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>2.893</v>
+        <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -39492,7 +39492,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -59332,7 +59332,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E546" s="5" t="n">
@@ -62300,7 +62300,7 @@
         </is>
       </c>
       <c r="E577" s="5" t="n">
-        <v>0.737038</v>
+        <v>-0.737038</v>
       </c>
       <c r="F577" s="5" t="n">
         <v>-3.883741</v>

--- a/output/pdf_financials_xlsx/EXN.xlsx
+++ b/output/pdf_financials_xlsx/EXN.xlsx
@@ -2001,16 +2001,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.935134</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>2.65011</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>2.499</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>2.893</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -2058,16 +2058,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.665596</v>
+        <v>2.60073</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.359</v>
+        <v>-2.70889</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11.246</v>
+        <v>13.745</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.506</v>
+        <v>3.399</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-3.618</v>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>10.38941694122755</v>
+        <v>16.2224623027185</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-18.23781649877484</v>
+        <v>-9.218928668663217</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>23.42428660695688</v>
+        <v>28.62945219745886</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1.394976980122956</v>
+        <v>9.370606236043338</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-10.85443417736709</v>
@@ -6080,13 +6080,13 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>2.532</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>2.499</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>2.893</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -7432,13 +7432,13 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.397</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.017</v>
       </c>
       <c r="P124" s="3" t="n">
         <v>0</v>
@@ -7487,13 +7487,13 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.397</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.017</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -28822,7 +28822,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -39492,7 +39496,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -48276,7 +48280,11 @@
           <t>General and administrative expenses 17.b</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -49568,7 +49576,11 @@
           <t>General and administrative expenses 18b</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -50758,7 +50770,11 @@
           <t>General and administrative expenses 16b</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
           <t>-</t>
@@ -51516,7 +51532,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -52466,7 +52482,11 @@
           <t>General and administrative expenses 15b</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>-</t>
@@ -53038,7 +53058,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -53882,7 +53902,11 @@
           <t>General and administrative expenses 12b</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -54640,7 +54664,11 @@
           <t>General and administrative expenses 11b</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
           <t>-</t>
@@ -59332,7 +59360,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E546" s="5" t="n">
@@ -60098,7 +60126,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E554" s="5" t="n">

--- a/output/pdf_financials_xlsx/EXN.xlsx
+++ b/output/pdf_financials_xlsx/EXN.xlsx
@@ -1075,16 +1075,16 @@
         <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>0.031</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>0.031</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.092</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.073</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -1947,16 +1947,16 @@
         <v>1.665596</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.359</v>
+        <v>-5.39</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>11.246</v>
+        <v>11.215</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.506</v>
+        <v>0.414</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.618</v>
+        <v>-3.691</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-20.282</v>
@@ -2061,16 +2061,16 @@
         <v>2.60073</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.70889</v>
+        <v>-2.73989</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>13.745</v>
+        <v>13.714</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.399</v>
+        <v>3.307</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.618</v>
+        <v>-3.691</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-20.282</v>
@@ -2118,16 +2118,16 @@
         <v>16.2224623027185</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-9.218928668663217</v>
+        <v>-9.324428260277703</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>28.62945219745886</v>
+        <v>28.56488231618412</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>9.370606236043338</v>
+        <v>9.116974057839164</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-10.85443417736709</v>
+        <v>-11.07344293771751</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-65.92127929274872</v>
@@ -55616,7 +55616,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -56952,7 +56956,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -58588,7 +58596,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
